--- a/test-cases/Parabank_Test_Cases.xlsx
+++ b/test-cases/Parabank_Test_Cases.xlsx
@@ -1,130 +1,58 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet sheetId="1" name="Test Cases" state="visible" r:id="rId4"/>
+    <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
-  <si>
-    <t>Test Case ID</t>
-  </si>
-  <si>
-    <t>Test Scenario</t>
-  </si>
-  <si>
-    <t>Test Steps</t>
-  </si>
-  <si>
-    <t>Test Data</t>
-  </si>
-  <si>
-    <t>Expected Result</t>
-  </si>
-  <si>
-    <t>Actual Result</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>TC001</t>
-  </si>
-  <si>
-    <t>User Registration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to Parabank registration page
-2. Fill in first name field
-3. Fill in last name field
-4. Fill in address field
-5. Fill in city field
-6. Fill in state field
-7. Fill in zip code field
-8. Fill in phone number field
-9. Fill in SSN field
-10. Fill in username field
-11. Fill in password field
-12. Fill in confirm password field
-13. Click Register button</t>
-  </si>
-  <si>
-    <t>firstName=John; lastName=Doe; address=123 Main St; city=Anytown; state=CA; zipCode=12345; phoneNumber=555-123-4567; ssn=123-45-6789; username=testuser; password=Test123456; confirmPassword=Test123456</t>
-  </si>
-  <si>
-    <t>Registration successful - "Your account was created successfully" message displayed</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>TC002</t>
-  </si>
-  <si>
-    <t>User Login</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to Parabank login page
-2. Enter username
-3. Enter password
-4. Click Login button</t>
-  </si>
-  <si>
-    <t>username=testuser; password=Test123456</t>
-  </si>
-  <si>
-    <t>Login successful - User redirected to Accounts page with Welcome message</t>
-  </si>
-  <si>
-    <t>TC003</t>
-  </si>
-  <si>
-    <t>Verify Account Balance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. After successful login, verify account balance is displayed
-2. Verify balance contains $ symbol</t>
-  </si>
-  <si>
-    <t>Account balance is displayed on the page with $ symbol</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
+      <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFDD00"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -132,37 +60,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -487,112 +396,1733 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G66"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="50" customWidth="1"/>
-    <col min="4" max="5" width="40" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="50.83203125" customWidth="1"/>
+    <col min="3" max="3" width="80.83203125" customWidth="1"/>
+    <col min="4" max="4" width="70.83203125" customWidth="1"/>
+    <col min="5" max="5" width="80.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>12</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Test Case ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Test Scenario</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Test Steps</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Test Data</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Expected Result</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Actual Result</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Status</v>
+      </c>
+    </row>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str">
+        <v>TC001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>User Registration with valid details</v>
+      </c>
+      <c r="C2" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Parabank registration page
+2. Fill in first name field (customer.firstName)
+3. Fill in last name field (customer.lastName)
+4. Fill in address field (customer.address.street)
+5. Fill in city field (customer.address.city)
+6. Fill in state field (customer.address.state)
+7. Fill in zip code field (customer.address.zipCode)
+8. Fill in phone number field (customer.phoneNumber)
+9. Fill in SSN field (customer.ssn)
+10. Fill in username field (customer.username)
+11. Fill in password field (customer.password)
+12. Fill in confirm password field (repeatedPassword)
+13. Click Register button (input[value="Register"])</v>
+      </c>
+      <c r="D2" t="str">
+        <v>firstName=John; lastName=Doe; address=123 Main St; city=Anytown; state=CA; zipCode=12345; phoneNumber=555-123-4567; ssn=123-45-6789; username=testuser; password=Test123456; confirmPassword=Test123456</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Registration successful. User redirected to dashboard. "Welcome" header and "Your account was created successfully. You are now logged in." message displayed.</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str">
+        <v>TC002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>User Login with valid credentials</v>
+      </c>
+      <c r="C3" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Parabank login page
+2. Enter username
+3. Enter password
+4. Click Login button</v>
+      </c>
+      <c r="D3" t="str">
+        <v>username=testuser; password=Test123456</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Login successful. User redirected to Accounts Overview page. Welcome message with full name displayed. Account services menu visible with 8 menu items.</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4" t="str">
+        <v>TC003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Verify Account Balance Display in Accounts Overview</v>
+      </c>
+      <c r="C4" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Login with valid credentials
+2. Verify Account Overview page is displayed
+3. Verify accountTable is visible with columns: Account, Balance*, Available Amount
+4. Verify balance is displayed in $XXX.XX format
+5. Verify Total row shows the sum of balances</v>
+      </c>
+      <c r="D4" t="str">
+        <v>N/A - Account data loaded dynamically via AJAX from REST API</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Account table (id="accountTable") displayed with account number (hyperlinked), balance (e.g. $515.50), and available amount. Total row shows aggregated balance in bold. Footer displays "Balance includes deposits" note.</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
+        <v>TC004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Registration - Empty First Name field</v>
+      </c>
+      <c r="C5" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to registration page
+2. Leave First Name field empty
+3. Fill all other mandatory fields with valid data
+4. Click Register button</v>
+      </c>
+      <c r="D5" t="str">
+        <v>firstName=(empty); lastName=Doe; address=123 Main St; city=Anytown; state=CA; zipCode=12345; phoneNumber=555-123-4567; ssn=123-45-6789; username=newuser1; password=Test123456; confirmPassword=Test123456</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Error message displayed or registration page remains with validation error on first name field.</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
+        <v>TC005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Registration - Password and Confirm Password mismatch</v>
+      </c>
+      <c r="C6" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to registration page
+2. Fill all fields with valid data
+3. Enter password as "Test123456"
+4. Enter confirm password as "Test654321" (different)
+5. Click Register button</v>
+      </c>
+      <c r="D6" t="str">
+        <v>firstName=John; lastName=Doe; address=123 Main St; city=Anytown; state=CA; zipCode=12345; phoneNumber=555-123-4567; ssn=123-45-6789; username=newuser2; password=Test123456; confirmPassword=Test654321</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Error message displayed: "Passwords do not match" or server-side validation error shown.</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str">
+        <v>TC006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Registration - Duplicate Username</v>
+      </c>
+      <c r="C7" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to registration page
+2. Fill all fields with valid data
+3. Enter username that already exists in the system
+4. Click Register button</v>
+      </c>
+      <c r="D7" t="str">
+        <v>firstName=Jane; lastName=Smith; address=456 Oak Ave; city=Springfield; state=IL; zipCode=62701; phoneNumber=555-987-6543; ssn=987-65-4321; username=testuser(already exists); password=Test123456; confirmPassword=Test123456</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Error message displayed: "This username already exists" or "Username already taken". Registration not allowed with duplicate username.</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8" t="str">
+        <v>TC007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Login with invalid credentials</v>
+      </c>
+      <c r="C8" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to login page
+2. Enter incorrect username
+3. Enter incorrect password
+4. Click Login button</v>
+      </c>
+      <c r="D8" t="str">
+        <v>username=wronguser; password=WrongPass123</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Error message displayed: "The username and password could not be verified" or similar login error. User remains on login page.</v>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9" t="str">
+        <v>TC008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Login with empty username and password</v>
+      </c>
+      <c r="C9" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to login page
+2. Leave username field empty
+3. Leave password field empty
+4. Click Login button</v>
+      </c>
+      <c r="D9" t="str">
+        <v>username=(empty); password=(empty)</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Error message displayed or login form shows validation errors for empty fields.</v>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str">
+        <v>TC009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Verify Account Overview table structure</v>
+      </c>
+      <c r="C10" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Login with valid credentials
+2. Navigate to Accounts Overview page
+3. Verify table id="accountTable" exists
+4. Verify thead contains: Account, Balance*, Available Amount
+5. Verify tbody contains account rows
+6. Verify tfoot contains footnote text</v>
+      </c>
+      <c r="D10" t="str">
+        <v>username=testuser; password=Test123456</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Table with id "accountTable" displayed. Header columns: Account, Balance*, Available Amount. Data rows show account links. Footer shows: "*Balance includes deposits that may be subject to holds"</v>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
+      <c r="A11" t="str">
+        <v>TC010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Verify Welcome message after login</v>
+      </c>
+      <c r="C11" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Login with valid credentials
+2. Verify left panel displays welcome message
+3. Verify welcome message contains users first and last name</v>
+      </c>
+      <c r="D11" t="str">
+        <v>username=testuser; password=Test123456</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Left panel displays "Welcome [First Name] [Last Name]" (e.g. "Welcome vimal sharma") confirming successful login with correct identity.</v>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str">
+        <v>TC011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Verify Account Services menu items</v>
+      </c>
+      <c r="C12" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Login with valid credentials
+2. Verify left panel shows "Account Services" heading
+3. Verify all 8 menu items are present and clickable</v>
+      </c>
+      <c r="D12" t="str">
+        <v>username=testuser; password=Test123456</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Account Services menu displayed with: Open New Account, Accounts Overview, Transfer Funds, Bill Pay, Find Transactions, Update Contact Info, Request Loan, Log Out. All links functional.</v>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
+      <c r="A13" t="str">
+        <v>TC012</v>
+      </c>
+      <c r="B13" t="str">
+        <v>User Logout functionality</v>
+      </c>
+      <c r="C13" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Login with valid credentials
+2. Click "Log Out" link from Account Services menu
+3. Verify redirect to home/login page
+4. Verify Account Services menu is no longer visible</v>
+      </c>
+      <c r="D13" t="str">
+        <v>username=testuser; password=Test123456</v>
+      </c>
+      <c r="E13" t="str">
+        <v>User logged out successfully. Redirected to home page. Account Services and Welcome message no longer displayed. Login form visible.</v>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="A14" t="str">
+        <v>TC013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Verify account number is hyperlinked</v>
+      </c>
+      <c r="C14" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Login with valid credentials
+2. Navigate to Accounts Overview
+3. Click on the account number link
+4. Verify navigation to Account Activity page</v>
+      </c>
+      <c r="D14" t="str">
+        <v>username=testuser; password=Test123456; Account ID=39096</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Account number is a hyperlink (href="activity.htm?id=39096"). Clicking navigates to Account Activity page for that account.</v>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
+      <c r="A15" t="str">
+        <v>TC014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Registration - All fields with special characters</v>
+      </c>
+      <c r="C15" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to registration page
+2. Fill in fields with special characters and numbers
+3. Submit the form</v>
+      </c>
+      <c r="D15" t="str">
+        <v>firstName=John123; lastName=Doe!@#; address=123 Main St #Apt 4B; city=Anytown-USA; state=CA; zipCode=12345-6789; phoneNumber=(555)123-4567; ssn=123-45-6789; username=newuser_special; password=Test@123!; confirmPassword=Test@123!</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Registration should succeed or appropriate validation error displayed based on field constraints.</v>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
+      <c r="A16" t="str">
+        <v>TC015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Full workflow: Register, Logout, Login, Verify Account</v>
+      </c>
+      <c r="C16" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Register new user with valid details
+2. Verify registration success message
+3. Logout from application
+4. Login with newly created credentials
+5. Verify welcome message with users name
+6. Verify account table displays balance</v>
+      </c>
+      <c r="D16" t="str">
+        <v>firstName=Alice; lastName=Johnson; address=789 Elm St; city=Boston; state=MA; zipCode=02101; phoneNumber=555-222-3333; ssn=222-33-4444; username=alice_j; password=AlicePass123; confirmPassword=AlicePass123</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Complete end-to-end flow works: Registration success -&gt; Logout -&gt; Login success -&gt; Welcome message displayed -&gt; Account overview with balance visible.</v>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str">
+        <v>TC016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Registration - Empty Last Name field</v>
+      </c>
+      <c r="C17" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to registration page
+2. Fill in all fields with valid data except Last Name
+3. Leave Last Name field empty
+4. Click Register button</v>
+      </c>
+      <c r="D17" t="str">
+        <v>firstName=John; lastName=(empty); address=123 Main St; city=Anytown; state=CA; zipCode=12345; phoneNumber=555-123-4567; ssn=123-45-6789; username=newuser_lname; password=Test123456; confirmPassword=Test123456</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Error message displayed indicating Last Name is required or registration fails with validation error. Registration not processed.</v>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="A18" t="str">
+        <v>TC017</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Registration - Empty Address field</v>
+      </c>
+      <c r="C18" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to registration page
+2. Fill in all fields with valid data except Address
+3. Leave Address field empty
+4. Click Register button</v>
+      </c>
+      <c r="D18" t="str">
+        <v>firstName=John; lastName=Doe; address=(empty); city=Anytown; state=CA; zipCode=12345; phoneNumber=555-123-4567; ssn=123-45-6789; username=newuser_addr; password=Test123456; confirmPassword=Test123456</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Error message displayed indicating Address is required or registration fails with validation error. Registration not processed.</v>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
+      <c r="A19" t="str">
+        <v>TC018</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Registration - Empty City field</v>
+      </c>
+      <c r="C19" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to registration page
+2. Fill in all fields with valid data except City
+3. Leave City field empty
+4. Click Register button</v>
+      </c>
+      <c r="D19" t="str">
+        <v>firstName=John; lastName=Doe; address=123 Main St; city=(empty); state=CA; zipCode=12345; phoneNumber=555-123-4567; ssn=123-45-6789; username=newuser_city; password=Test123456; confirmPassword=Test123456</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Error message displayed indicating City is required or registration fails with validation error. Registration not processed.</v>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="A20" t="str">
+        <v>TC019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Registration - Empty State field</v>
+      </c>
+      <c r="C20" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to registration page
+2. Fill in all fields with valid data except State
+3. Leave State field empty
+4. Click Register button</v>
+      </c>
+      <c r="D20" t="str">
+        <v>firstName=John; lastName=Doe; address=123 Main St; city=Anytown; state=(empty); zipCode=12345; phoneNumber=555-123-4567; ssn=123-45-6789; username=newuser_state; password=Test123456; confirmPassword=Test123456</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Error message displayed indicating State is required or registration fails with validation error. Registration not processed.</v>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str">
+        <v>TC020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Registration - Empty Zip Code field</v>
+      </c>
+      <c r="C21" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to registration page
+2. Fill in all fields with valid data except Zip Code
+3. Leave Zip Code field empty
+4. Click Register button</v>
+      </c>
+      <c r="D21" t="str">
+        <v>firstName=John; lastName=Doe; address=123 Main St; city=Anytown; state=CA; zipCode=(empty); phoneNumber=555-123-4567; ssn=123-45-6789; username=newuser_zip; password=Test123456; confirmPassword=Test123456</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Error message displayed indicating Zip Code is required or registration fails with validation error. Registration not processed.</v>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>TC021</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Registration - Empty Phone Number field</v>
+      </c>
+      <c r="C22" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to registration page
+2. Fill in all fields with valid data except Phone Number
+3. Leave Phone Number field empty
+4. Click Register button</v>
+      </c>
+      <c r="D22" t="str">
+        <v>firstName=John; lastName=Doe; address=123 Main St; city=Anytown; state=CA; zipCode=12345; phoneNumber=(empty); ssn=123-45-6789; username=newuser_phone; password=Test123456; confirmPassword=Test123456</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Error message displayed indicating Phone Number is required or registration fails with validation error. Registration not processed.</v>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="A23" t="str">
+        <v>TC022</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Registration - Empty SSN field</v>
+      </c>
+      <c r="C23" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to registration page
+2. Fill in all fields with valid data except SSN
+3. Leave SSN field empty
+4. Click Register button</v>
+      </c>
+      <c r="D23" t="str">
+        <v>firstName=John; lastName=Doe; address=123 Main St; city=Anytown; state=CA; zipCode=12345; phoneNumber=555-123-4567; ssn=(empty); username=newuser_ssn; password=Test123456; confirmPassword=Test123456</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Error message displayed indicating SSN is required or registration fails with validation error. Registration not processed.</v>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24" xml:space="preserve">
+      <c r="A24" t="str">
+        <v>TC023</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Registration - Empty Username field</v>
+      </c>
+      <c r="C24" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to registration page
+2. Fill in all fields with valid data except Username
+3. Leave Username field empty
+4. Click Register button</v>
+      </c>
+      <c r="D24" t="str">
+        <v>firstName=John; lastName=Doe; address=123 Main St; city=Anytown; state=CA; zipCode=12345; phoneNumber=555-123-4567; ssn=123-45-6789; username=(empty); password=Test123456; confirmPassword=Test123456</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Error message displayed indicating Username is required or registration fails with validation error. Registration not processed.</v>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="A25" t="str">
+        <v>TC024</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Registration - Empty Password field</v>
+      </c>
+      <c r="C25" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to registration page
+2. Fill in all fields with valid data except Password
+3. Leave Password field empty
+4. Enter valid Confirm Password
+5. Click Register button</v>
+      </c>
+      <c r="D25" t="str">
+        <v>firstName=John; lastName=Doe; address=123 Main St; city=Anytown; state=CA; zipCode=12345; phoneNumber=555-123-4567; ssn=123-45-6789; username=newuser_pwd; password=(empty); confirmPassword=Test123456</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Error message displayed indicating Password is required or passwords do not match. Registration not processed.</v>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="A26" t="str">
+        <v>TC025</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Registration - Empty Confirm Password field</v>
+      </c>
+      <c r="C26" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to registration page
+2. Fill in all fields with valid data
+3. Enter valid Password
+4. Leave Confirm Password field empty
+5. Click Register button</v>
+      </c>
+      <c r="D26" t="str">
+        <v>firstName=John; lastName=Doe; address=123 Main St; city=Anytown; state=CA; zipCode=12345; phoneNumber=555-123-4567; ssn=123-45-6789; username=newuser_cpwd; password=Test123456; confirmPassword=(empty)</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Error message displayed indicating Confirm Password is required or passwords do not match. Registration not processed.</v>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27" t="str">
+        <v>TC026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Registration - Password with minimum length (1 character)</v>
+      </c>
+      <c r="C27" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to registration page
+2. Fill in all fields with valid data
+3. Enter password with single character
+4. Enter same single character in Confirm Password
+5. Click Register button</v>
+      </c>
+      <c r="D27" t="str">
+        <v>firstName=John; lastName=Doe; address=123 Main St; city=Anytown; state=CA; zipCode=12345; phoneNumber=555-123-4567; ssn=123-45-6789; username=newuser_minpwd; password=a; confirmPassword=a</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Registration should fail with password length validation error or succeed based on system minimum password requirements.</v>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28" xml:space="preserve">
+      <c r="A28" t="str">
+        <v>TC027</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Registration - Password with maximum length boundary</v>
+      </c>
+      <c r="C28" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to registration page
+2. Fill in all fields with valid data
+3. Enter password with 128 characters (or system max)
+4. Enter same password in Confirm Password
+5. Click Register button</v>
+      </c>
+      <c r="D28" t="str">
+        <v>firstName=John; lastName=Doe; address=123 Main St; city=Anytown; state=CA; zipCode=12345; phoneNumber=555-123-4567; ssn=123-45-6789; username=newuser_maxpwd; password=aB1! (repeated to max length); confirmPassword=aB1! (repeated to max length)</v>
+      </c>
+      <c r="E28" t="str">
+        <v>System should properly handle long passwords. Either truncation or acceptance with appropriate response.</v>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29" t="str">
+        <v>TC028</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Registration - SSN with invalid format (alphabetic characters)</v>
+      </c>
+      <c r="C29" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to registration page
+2. Fill in all fields with valid data
+3. Enter SSN with alphabetic characters instead of digits
+4. Click Register button</v>
+      </c>
+      <c r="D29" t="str">
+        <v>firstName=John; lastName=Doe; address=123 Main St; city=Anytown; state=CA; zipCode=12345; phoneNumber=555-123-4567; ssn=ABCDEFGHI; username=newuser_ssnfmt; password=Test123456; confirmPassword=Test123456</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Error message displayed indicating invalid SSN format. SSN should only accept numeric values.</v>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30" xml:space="preserve">
+      <c r="A30" t="str">
+        <v>TC029</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Registration - SSN with special characters</v>
+      </c>
+      <c r="C30" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to registration page
+2. Fill in all fields with valid data
+3. Enter SSN with special characters like #$%@
+4. Click Register button</v>
+      </c>
+      <c r="D30" t="str">
+        <v>firstName=John; lastName=Doe; address=123 Main St; city=Anytown; state=CA; zipCode=12345; phoneNumber=555-123-4567; ssn=###-##-####; username=newuser_ssnspc; password=Test123456; confirmPassword=Test123456</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Error message displayed indicating invalid SSN format or system rejects special characters in SSN field.</v>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
+      <c r="A31" t="str">
+        <v>TC030</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Registration - Zip Code with alphabetic characters</v>
+      </c>
+      <c r="C31" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to registration page
+2. Fill in all fields with valid data
+3. Enter alphabetic characters in Zip Code field
+4. Click Register button</v>
+      </c>
+      <c r="D31" t="str">
+        <v>firstName=John; lastName=Doe; address=123 Main St; city=Anytown; state=CA; zipCode=ABCDE; phoneNumber=555-123-4567; ssn=123-45-6789; username=newuser_zipalpha; password=Test123456; confirmPassword=Test123456</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Error message displayed indicating Zip Code must be numeric. Registration not processed.</v>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32" xml:space="preserve">
+      <c r="A32" t="str">
+        <v>TC031</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Registration - Zip Code with 9-digit format (XXXXX-XXXX)</v>
+      </c>
+      <c r="C32" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to registration page
+2. Fill in all fields with valid data
+3. Enter Zip Code in extended 9-digit format with hyphen
+4. Click Register button</v>
+      </c>
+      <c r="D32" t="str">
+        <v>firstName=John; lastName=Doe; address=123 Main St; city=Anytown; state=CA; zipCode=12345-6789; phoneNumber=555-123-4567; ssn=123-45-6789; username=newuser_zip9; password=Test123456; confirmPassword=Test123456</v>
+      </c>
+      <c r="E32" t="str">
+        <v>System should accept 9-digit zip code format (XXXXX-XXXX) and process registration successfully or display validation error.</v>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33" xml:space="preserve">
+      <c r="A33" t="str">
+        <v>TC032</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Registration - Phone Number with non-numeric characters</v>
+      </c>
+      <c r="C33" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to registration page
+2. Fill in all fields with valid data
+3. Enter Phone Number with alphabetic characters
+4. Click Register button</v>
+      </c>
+      <c r="D33" t="str">
+        <v>firstName=John; lastName=Doe; address=123 Main St; city=Anytown; state=CA; zipCode=12345; phoneNumber=ABCDEFGHIJ; ssn=123-45-6789; username=newuser_phnalpha; password=Test123456; confirmPassword=Test123456</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Error message displayed indicating Phone Number must be numeric. Registration not processed.</v>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34" xml:space="preserve">
+      <c r="A34" t="str">
+        <v>TC033</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Registration - First Name with maximum length characters</v>
+      </c>
+      <c r="C34" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to registration page
+2. Enter First Name with 100 characters (or boundary)
+3. Fill in all other fields with valid data
+4. Click Register button</v>
+      </c>
+      <c r="D34" t="str">
+        <v>firstName=(100-character string); lastName=Doe; address=123 Main St; city=Anytown; state=CA; zipCode=12345; phoneNumber=555-123-4567; ssn=123-45-6789; username=newuser_maxfn; password=Test123456; confirmPassword=Test123456</v>
+      </c>
+      <c r="E34" t="str">
+        <v>System should accept or truncate the field to its maximum allowed length. Registration should succeed or display appropriate truncation/validation message.</v>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35" xml:space="preserve">
+      <c r="A35" t="str">
+        <v>TC034</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Registration - SQL Injection attempt in Username field</v>
+      </c>
+      <c r="C35" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to registration page
+2. Fill in all fields with valid data
+3. Enter SQL injection string in Username field
+4. Click Register button</v>
+      </c>
+      <c r="D35" t="str">
+        <v>firstName=John; lastName=Doe; address=123 Main St; city=Anytown; state=CA; zipCode=12345; phoneNumber=555-123-4567; ssn=123-45-6789; username=' OR 1=1--; password=Test123456; confirmPassword=Test123456</v>
+      </c>
+      <c r="E35" t="str">
+        <v>System should escape/sanitize the SQL injection attempt. Registration should either fail with validation error or succeed with the literal string without SQL execution.</v>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36" xml:space="preserve">
+      <c r="A36" t="str">
+        <v>TC035</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Registration - XSS attempt in First Name field</v>
+      </c>
+      <c r="C36" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to registration page
+2. Enter XSS script tag in First Name field
+3. Fill in all other fields with valid data
+4. Click Register button</v>
+      </c>
+      <c r="D36" t="str">
+        <v>firstName=&lt;script&gt;alert('XSS')&lt;/script&gt;; lastName=Doe; address=123 Main St; city=Anytown; state=CA; zipCode=12345; phoneNumber=555-123-4567; ssn=123-45-6789; username=newuser_xss; password=Test123456; confirmPassword=Test123456</v>
+      </c>
+      <c r="E36" t="str">
+        <v>System should sanitize HTML/JavaScript input. Script tag should be escaped or rejected. No script execution should occur on any page displaying the name.</v>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37" xml:space="preserve">
+      <c r="A37" t="str">
+        <v>TC036</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Accounts Overview - Verify AJAX API endpoint returns 404/error</v>
+      </c>
+      <c r="C37" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Login with valid credentials
+2. Navigate to Accounts Overview page
+3. Simulate API failure (modify request or use test data causing error)
+4. Verify error handling</v>
+      </c>
+      <c r="D37" t="str">
+        <v>username=testuser; password=Test123456; Trigger API error from services_proxy/bank/customers/{id}/accounts</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Error div (id='showError') should be displayed. 'An internal error has occurred and has been logged.' message shown. Overview div (id='showOverview') hidden.</v>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="A38" t="str">
+        <v>TC037</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Accounts Overview - Verify available balance for negative account balance</v>
+      </c>
+      <c r="C38" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Login with credentials that have an account with negative balance
+2. Navigate to Accounts Overview page
+3. Verify Available Amount column
+4. Verify the available balance calculation logic</v>
+      </c>
+      <c r="D38" t="str">
+        <v>username=testuser_negative; password=Test123456; Account with negative balance</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Available Amount should display as $0.00 for accounts with negative balance (per JS logic: availableBalance = balance &lt; 0 ? 0 : balance). Balance column shows the actual negative amount.</v>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39" xml:space="preserve">
+      <c r="A39" t="str">
+        <v>TC038</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Accounts Overview - Verify zero balance account display</v>
+      </c>
+      <c r="C39" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Login with credentials that have a zero-balance account
+2. Navigate to Accounts Overview page
+3. Verify zero balance is correctly formatted</v>
+      </c>
+      <c r="D39" t="str">
+        <v>username=testuser_zero; password=Test123456; Account with $0.00 balance</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Balance displayed as $0.00. Available Amount also $0.00. Total row correctly aggregates zero with other accounts.</v>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40" xml:space="preserve">
+      <c r="A40" t="str">
+        <v>TC039</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Accounts Overview - Verify multiple accounts aggregation</v>
+      </c>
+      <c r="C40" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Login with credentials having multiple accounts
+2. Navigate to Accounts Overview page
+3. Verify all accounts are listed
+4. Verify Total row correctly sums all balances</v>
+      </c>
+      <c r="D40" t="str">
+        <v>username=testuser_multi; password=Test123456; Multiple accounts with varying balances</v>
+      </c>
+      <c r="E40" t="str">
+        <v>All accounts displayed as separate rows. Total row shows correct sum of all account balances in bold. Footer text visible.</v>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41" xml:space="preserve">
+      <c r="A41" t="str">
+        <v>TC040</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Accounts Overview - Verify AJAX timeout handling</v>
+      </c>
+      <c r="C41" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Login with valid credentials
+2. Navigate to Accounts Overview page
+3. Simulate slow network causing AJAX timeout (&gt;30 seconds)
+4. Verify error state</v>
+      </c>
+      <c r="D41" t="str">
+        <v>username=testuser; password=Test123456; Network throttled to cause timeout</v>
+      </c>
+      <c r="E41" t="str">
+        <v>After 30 seconds timeout, error handler should trigger. Error div (id='showError') displayed. Console logs error message.</v>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42" xml:space="preserve">
+      <c r="A42" t="str">
+        <v>TC041</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Verify Top Panel - Admin link navigates to Admin page</v>
+      </c>
+      <c r="C42" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to any page (Home/Login)
+2. Click on Admin image link (href='admin.htm') in top panel
+3. Verify navigation</v>
+      </c>
+      <c r="D42" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Clicking the admin image (img with class='admin') navigates to admin.htm page.</v>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
+      <c r="A43" t="str">
+        <v>TC042</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Verify Top Panel - Logo navigates to Home page</v>
+      </c>
+      <c r="C43" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to any page
+2. Click on ParaBank logo (img with class='logo') in top panel
+3. Verify navigation to index.htm</v>
+      </c>
+      <c r="D43" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Clicking the ParaBank logo (href='index.htm') navigates back to the home page.</v>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44" xml:space="preserve">
+      <c r="A44" t="str">
+        <v>TC043</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Verify Top Panel - Caption text 'Experience the difference'</v>
+      </c>
+      <c r="C44" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Home page
+2. Verify top panel contains caption element
+3. Verify caption text content</v>
+      </c>
+      <c r="D44" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Top panel displays caption text: 'Experience the difference' inside a p tag with class='caption'.</v>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45" xml:space="preserve">
+      <c r="A45" t="str">
+        <v>TC044</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Verify Left Menu - About Us link</v>
+      </c>
+      <c r="C45" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to any page
+2. Click 'About Us' link from left menu
+3. Verify navigation</v>
+      </c>
+      <c r="D45" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Clicking 'About Us' link (href='about.htm') navigates to About Us page.</v>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46" xml:space="preserve">
+      <c r="A46" t="str">
+        <v>TC045</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Verify Left Menu - Services link</v>
+      </c>
+      <c r="C46" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to any page
+2. Click 'Services' link from left menu
+3. Verify navigation</v>
+      </c>
+      <c r="D46" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Clicking 'Services' link (href='services.htm') navigates to Services page.</v>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47" xml:space="preserve">
+      <c r="A47" t="str">
+        <v>TC046</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Verify Left Menu - Products link (external URL)</v>
+      </c>
+      <c r="C47" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to any page
+2. Click 'Products' link from left menu
+3. Verify navigation to external Parasoft products page</v>
+      </c>
+      <c r="D47" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Clicking 'Products' link navigates to external URL: http://www.parasoft.com/jsp/products.jsp (opens in same window or new tab).</v>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48" xml:space="preserve">
+      <c r="A48" t="str">
+        <v>TC047</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Verify Left Menu - Locations link (external URL)</v>
+      </c>
+      <c r="C48" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to any page
+2. Click 'Locations' link from left menu
+3. Verify navigation to external Parasoft contact page</v>
+      </c>
+      <c r="D48" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Clicking 'Locations' link navigates to external URL: http://www.parasoft.com/jsp/pr/contacts.jsp.</v>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49" xml:space="preserve">
+      <c r="A49" t="str">
+        <v>TC048</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Verify Header Panel - Home button</v>
+      </c>
+      <c r="C49" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to any page
+2. Click 'home' button from header panel (ul.button &gt; li.home)
+3. Verify navigation</v>
+      </c>
+      <c r="D49" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Clicking 'home' button navigates to index.htm.</v>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50" xml:space="preserve">
+      <c r="A50" t="str">
+        <v>TC049</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Verify Header Panel - About button</v>
+      </c>
+      <c r="C50" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to any page
+2. Click 'about' button from header panel (ul.button &gt; li.aboutus)
+3. Verify navigation</v>
+      </c>
+      <c r="D50" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Clicking 'about' button navigates to about.htm.</v>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51" xml:space="preserve">
+      <c r="A51" t="str">
+        <v>TC050</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Verify Header Panel - Contact button</v>
+      </c>
+      <c r="C51" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to any page
+2. Click 'contact' button from header panel (ul.button &gt; li.contact)
+3. Verify navigation</v>
+      </c>
+      <c r="D51" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Clicking 'contact' button navigates to contact.htm.</v>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52" xml:space="preserve">
+      <c r="A52" t="str">
+        <v>TC051</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Verify Footer - Home link</v>
+      </c>
+      <c r="C52" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to any page
+2. Scroll to footer (div id='footerPanel')
+3. Click 'Home' link in footer
+4. Verify navigation</v>
+      </c>
+      <c r="D52" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Footer 'Home' link navigates to index.htm. Footer displayed correctly with copyright and visit links.</v>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53" xml:space="preserve">
+      <c r="A53" t="str">
+        <v>TC052</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Verify Footer - Copyright text</v>
+      </c>
+      <c r="C53" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to any page
+2. Scroll to footer
+3. Verify copyright text is displayed correctly</v>
+      </c>
+      <c r="D53" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Footer displays copyright text: '© Parasoft. All rights reserved.' in a p tag with class='copyright'.</v>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54" xml:space="preserve">
+      <c r="A54" t="str">
+        <v>TC053</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Verify Footer - Visit us link (external)</v>
+      </c>
+      <c r="C54" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to any page
+2. Scroll to footer
+3. Click 'www.parasoft.com' link in footer
+4. Verify navigation to external website</v>
+      </c>
+      <c r="D54" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Clicking 'www.parasoft.com' in footer navigates to http://www.parasoft.com/ in a new tab/window.</v>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55" xml:space="preserve">
+      <c r="A55" t="str">
+        <v>TC054</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Registration - Phone Number with valid formats (with dashes, brackets, spaces)</v>
+      </c>
+      <c r="C55" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to registration page
+2. Fill in all fields with valid data
+3. Enter Phone Number with various valid formats: (555) 123-4567, 555-123-4567, 5551234567
+4. Click Register button</v>
+      </c>
+      <c r="D55" t="str">
+        <v>firstName=John; lastName=Doe; address=123 Main St; city=Anytown; state=CA; zipCode=12345; phoneNumber=(555) 123-4567; ssn=123-45-6789; username=newuser_phnfmt; password=Test123456; confirmPassword=Test123456</v>
+      </c>
+      <c r="E55" t="str">
+        <v>System should accept phone numbers in common US formats (with parentheses, dashes, spaces, or without separators). Registration succeeds.</v>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56" xml:space="preserve">
+      <c r="A56" t="str">
+        <v>TC055</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Registration - All fields with leading and trailing spaces</v>
+      </c>
+      <c r="C56" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to registration page
+2. Fill in all fields with values containing leading/trailing spaces
+3. Click Register button
+4. Verify welcome message after login shows trimmed name</v>
+      </c>
+      <c r="D56" t="str">
+        <v>firstName='  John  '; lastName='  Doe  '; address='  123 Main St  '; city='  Anytown  '; state='  CA  '; zipCode='  12345  '; phoneNumber='  555-123-4567  '; ssn='  123-45-6789  '; username='  spaceduser  '; password='  Test123456  '; confirmPassword='  Test123456  '</v>
+      </c>
+      <c r="E56" t="str">
+        <v>System should trim leading/trailing spaces from all fields. Registration succeeds. Welcome message displays properly trimmed name (e.g., 'Welcome John Doe').</v>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57" xml:space="preserve">
+      <c r="A57" t="str">
+        <v>TC056</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Registration - Verify form reset after failed submission</v>
+      </c>
+      <c r="C57" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to registration page
+2. Submit form with empty required fields
+3. Verify form state after error message
+4. Check if previously entered data is preserved or cleared</v>
+      </c>
+      <c r="D57" t="str">
+        <v>firstName=(empty); lastName=Doe; address=123 Main St; city=Anytown; state=CA; zipCode=12345; phoneNumber=555-123-4567; ssn=123-45-6789; username=newuser_reset; password=Test123456; confirmPassword=Test123456</v>
+      </c>
+      <c r="E57" t="str">
+        <v>Form should preserve previously entered data (except password fields) after a failed submission attempt so user can correct errors without retyping everything.</v>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58" xml:space="preserve">
+      <c r="A58" t="str">
+        <v>TC057</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Verify Account Services - Open New Account link</v>
+      </c>
+      <c r="C58" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Login with valid credentials
+2. Click 'Open New Account' link from Account Services
+3. Verify navigation to openaccount.htm</v>
+      </c>
+      <c r="D58" t="str">
+        <v>username=testuser; password=Test123456</v>
+      </c>
+      <c r="E58" t="str">
+        <v>Clicking 'Open New Account' navigates to openaccount.htm page where new account creation form is displayed.</v>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59" xml:space="preserve">
+      <c r="A59" t="str">
+        <v>TC058</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Verify Account Services - Transfer Funds link</v>
+      </c>
+      <c r="C59" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Login with valid credentials
+2. Click 'Transfer Funds' link from Account Services
+3. Verify navigation to transfer.htm</v>
+      </c>
+      <c r="D59" t="str">
+        <v>username=testuser; password=Test123456</v>
+      </c>
+      <c r="E59" t="str">
+        <v>Clicking 'Transfer Funds' navigates to transfer.htm page showing fund transfer form with 'From Account', 'To Account', and 'Amount' fields.</v>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60" xml:space="preserve">
+      <c r="A60" t="str">
+        <v>TC059</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Verify Account Services - Bill Pay link</v>
+      </c>
+      <c r="C60" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Login with valid credentials
+2. Click 'Bill Pay' link from Account Services
+3. Verify navigation to billpay.htm</v>
+      </c>
+      <c r="D60" t="str">
+        <v>username=testuser; password=Test123456</v>
+      </c>
+      <c r="E60" t="str">
+        <v>Clicking 'Bill Pay' navigates to billpay.htm page displaying bill payment form.</v>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61" xml:space="preserve">
+      <c r="A61" t="str">
+        <v>TC060</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Verify Account Services - Find Transactions link</v>
+      </c>
+      <c r="C61" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Login with valid credentials
+2. Click 'Find Transactions' link from Account Services
+3. Verify navigation to findtrans.htm</v>
+      </c>
+      <c r="D61" t="str">
+        <v>username=testuser; password=Test123456</v>
+      </c>
+      <c r="E61" t="str">
+        <v>Clicking 'Find Transactions' navigates to findtrans.htm page showing transaction search/filter form.</v>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62" xml:space="preserve">
+      <c r="A62" t="str">
+        <v>TC061</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Verify Account Services - Update Contact Info link</v>
+      </c>
+      <c r="C62" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Login with valid credentials
+2. Click 'Update Contact Info' link from Account Services
+3. Verify navigation to updateprofile.htm</v>
+      </c>
+      <c r="D62" t="str">
+        <v>username=testuser; password=Test123456</v>
+      </c>
+      <c r="E62" t="str">
+        <v>Clicking 'Update Contact Info' navigates to updateprofile.htm page with pre-filled contact information form.</v>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63" xml:space="preserve">
+      <c r="A63" t="str">
+        <v>TC062</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Verify Account Services - Request Loan link</v>
+      </c>
+      <c r="C63" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Login with valid credentials
+2. Click 'Request Loan' link from Account Services
+3. Verify navigation to requestloan.htm</v>
+      </c>
+      <c r="D63" t="str">
+        <v>username=testuser; password=Test123456</v>
+      </c>
+      <c r="E63" t="str">
+        <v>Clicking 'Request Loan' navigates to requestloan.htm page displaying loan application form.</v>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64" xml:space="preserve">
+      <c r="A64" t="str">
+        <v>TC063</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Verify registration form has all required elements from DOM</v>
+      </c>
+      <c r="C64" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to registration page
+2. Verify form id='customerForm' exists with method='post' and action='register.htm'
+3. Verify table with class='form2' contains all 11 input fields and 1 submit button
+4. Verify all input fields have correct id, name, and class attributes</v>
+      </c>
+      <c r="D64" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E64" t="str">
+        <v>Form contains: customer.firstName, customer.lastName, customer.address.street, customer.address.city, customer.address.state, customer.address.zipCode, customer.phoneNumber, customer.ssn, customer.username, customer.password, repeatedPassword. All have class='input' and correct name/id. Submit button has class='button' and value='Register'.</v>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65" xml:space="preserve">
+      <c r="A65" t="str">
+        <v>TC064</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Verify Accounts Overview page DOM structure after successful login</v>
+      </c>
+      <c r="C65" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Login with valid credentials
+2. Verify div with id='overviewAccountsApp' exists
+3. Verify div id='showOverview' and div id='showError' exist
+4. Verify showOverview is visible and showError is hidden
+5. Verify table id='accountTable' has proper structure (thead, tbody, tfoot)</v>
+      </c>
+      <c r="D65" t="str">
+        <v>username=testuser; password=Test123456</v>
+      </c>
+      <c r="E65" t="str">
+        <v>overviewAccountsApp div present. showOverview displayed. showError not visible (display:none). accountTable has gradient-style class with thead (Account, Balance*, Available Amount), tbody with account rows, tfoot with footnote text.</v>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66" xml:space="preserve">
+      <c r="A66" t="str">
+        <v>TC065</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Verify 'Balance* includes deposits' footnote in Account Overview</v>
+      </c>
+      <c r="C66" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Login with valid credentials
+2. Navigate to Accounts Overview page
+3. Scroll to table footer
+4. Verify footnote text matches exactly</v>
+      </c>
+      <c r="D66" t="str">
+        <v>username=testuser; password=Test123456</v>
+      </c>
+      <c r="E66" t="str">
+        <v>Table footer (tfoot) displays text: '*Balance includes deposits that may be subject to holds' in a single td with colspan='3'.</v>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G66"/>
+  </ignoredErrors>
 </worksheet>
 </file>